--- a/data/trans_bre/IP1002-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP1002-Habitat-trans_bre.xlsx
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 3,42</t>
+          <t>-0,91; 3,73</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,0; 1,25</t>
+          <t>-4,62; 1,41</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 2,28</t>
+          <t>-0,87; 2,34</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,18; 3,77</t>
+          <t>-3,24; 3,84</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,7 +685,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 122,12</t>
+          <t>-89,55; 175,26</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -760,37 +760,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 2,88</t>
+          <t>-0,72; 2,81</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,27; 1,42</t>
+          <t>-3,6; 1,29</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 1,16</t>
+          <t>-2,76; 1,32</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 1,18</t>
+          <t>-1,85; 1,17</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-60,92; —</t>
+          <t>-73,72; 846,35</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-80,94; 153,33</t>
+          <t>-82,49; 159,77</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-83,76; 157,27</t>
+          <t>-84,84; 177,43</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 2,25</t>
+          <t>-1,41; 2,38</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,97; 1,73</t>
+          <t>-3,72; 1,52</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 1,04</t>
+          <t>-2,83; 0,9</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 2,05</t>
+          <t>-3,62; 2,18</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-83,23; 135,17</t>
+          <t>-84,2; 117,72</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-89,42; 294,61</t>
+          <t>-86,24; 306,81</t>
         </is>
       </c>
     </row>
@@ -960,27 +960,27 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,91; 0,88</t>
+          <t>-3,27; 0,85</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 1,49</t>
+          <t>-1,55; 1,56</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 1,92</t>
+          <t>-1,6; 2,1</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 1,36</t>
+          <t>-1,63; 1,36</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 497,35</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 1,12</t>
+          <t>-0,72; 1,22</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 0,29</t>
+          <t>-2,17; 0,27</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 0,58</t>
+          <t>-1,24; 0,64</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 1,12</t>
+          <t>-1,44; 0,89</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-50,8; 155,5</t>
+          <t>-46,23; 175,26</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-66,55; 21,2</t>
+          <t>-69,25; 19,17</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-68,12; 70,29</t>
+          <t>-64,23; 74,74</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-62,83; 142,67</t>
+          <t>-65,92; 110,48</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP1002-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP1002-Habitat-trans_bre.xlsx
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 3,73</t>
+          <t>-0,88; 3,78</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,62; 1,41</t>
+          <t>-4,67; 1,31</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 2,34</t>
+          <t>-0,88; 2,34</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 3,84</t>
+          <t>-3,36; 3,97</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,7 +685,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-89,55; 175,26</t>
+          <t>-100,0; 110,62</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -760,37 +760,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 2,81</t>
+          <t>-0,73; 2,78</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 1,29</t>
+          <t>-3,42; 1,19</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,76; 1,32</t>
+          <t>-3,05; 1,16</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 1,17</t>
+          <t>-1,76; 1,18</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-73,72; 846,35</t>
+          <t>-68,56; 984,65</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-82,49; 159,77</t>
+          <t>-86,85; 107,19</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-84,84; 177,43</t>
+          <t>-87,79; 148,66</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 2,38</t>
+          <t>-1,45; 2,38</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,72; 1,52</t>
+          <t>-3,72; 1,53</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,83; 0,9</t>
+          <t>-2,69; 1,09</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,62; 2,18</t>
+          <t>-3,52; 2,08</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-84,2; 117,72</t>
+          <t>-83,38; 135,87</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-86,24; 306,81</t>
+          <t>-88,74; 272,69</t>
         </is>
       </c>
     </row>
@@ -960,22 +960,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,27; 0,85</t>
+          <t>-3,11; 0,65</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 1,56</t>
+          <t>-1,67; 1,72</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 2,1</t>
+          <t>-1,49; 2,01</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 1,36</t>
+          <t>-1,79; 1,09</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 1,22</t>
+          <t>-0,81; 1,19</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 0,27</t>
+          <t>-2,09; 0,31</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 0,64</t>
+          <t>-1,18; 0,7</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 0,89</t>
+          <t>-1,17; 1,01</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-46,23; 175,26</t>
+          <t>-50,99; 175,99</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-69,25; 19,17</t>
+          <t>-67,84; 18,37</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-64,23; 74,74</t>
+          <t>-63,3; 88,97</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-65,92; 110,48</t>
+          <t>-60,81; 137,71</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP1002-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP1002-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,49</t>
+          <t>0,75</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>29,09%</t>
+          <t>53,64%</t>
         </is>
       </c>
     </row>
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 3,78</t>
+          <t>-0,83; 3,42</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,67; 1,31</t>
+          <t>-5,0; 1,25</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 2,34</t>
+          <t>-0,88; 2,28</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,36; 3,97</t>
+          <t>-2,03; 4,03</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,7 +685,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 110,62</t>
+          <t>-100,0; 122,12</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-0,19</t>
+          <t>-0,29</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-18,81%</t>
+          <t>-25,58%</t>
         </is>
       </c>
     </row>
@@ -760,37 +760,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 2,78</t>
+          <t>-0,7; 2,88</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,42; 1,19</t>
+          <t>-3,27; 1,42</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 1,16</t>
+          <t>-2,94; 1,16</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 1,18</t>
+          <t>-2,01; 1,23</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-68,56; 984,65</t>
+          <t>-60,92; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-86,85; 107,19</t>
+          <t>-80,94; 153,33</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-87,79; 148,66</t>
+          <t>-83,76; 157,27</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-0,52</t>
+          <t>-0,22</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-22,43%</t>
+          <t>-9,05%</t>
         </is>
       </c>
     </row>
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 2,38</t>
+          <t>-1,63; 2,25</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,72; 1,53</t>
+          <t>-3,97; 1,73</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 1,09</t>
+          <t>-2,66; 1,04</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,52; 2,08</t>
+          <t>-3,67; 2,8</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-83,38; 135,87</t>
+          <t>-83,23; 135,17</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-88,74; 272,69</t>
+          <t>-88,22; 495,2</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-0,1</t>
+          <t>-0,18</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-12,75%</t>
+          <t>-23,24%</t>
         </is>
       </c>
     </row>
@@ -960,27 +960,27 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,11; 0,65</t>
+          <t>-2,91; 0,88</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 1,72</t>
+          <t>-1,76; 1,49</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 2,01</t>
+          <t>-1,42; 1,92</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 1,09</t>
+          <t>-1,98; 1,03</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 497,35</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-0,09</t>
+          <t>-0,04</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-6,64%</t>
+          <t>-2,76%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 1,19</t>
+          <t>-0,76; 1,12</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 0,31</t>
+          <t>-2,07; 0,29</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 0,7</t>
+          <t>-1,22; 0,58</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 1,01</t>
+          <t>-1,28; 1,19</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-50,99; 175,99</t>
+          <t>-50,8; 155,5</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-67,84; 18,37</t>
+          <t>-66,55; 21,2</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-63,3; 88,97</t>
+          <t>-68,12; 70,29</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-60,81; 137,71</t>
+          <t>-63,21; 158,04</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP1002-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP1002-Habitat-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,181 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>1,03</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-1,65</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,47</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,75</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>118,36%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-49,64%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>105,84%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>53,64%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>1.027794417567759</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-1.650498487297915</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.4663018152321207</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>0.746930798649784</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>1.183592263764256</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>-0.4963948264244613</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>1.058392279523618</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>0.5364441867561586</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-0,83; 3,42</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-5,0; 1,25</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-0,88; 2,28</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-2,03; 4,03</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 122,12</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-0.8273362604950207</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-4.997161835154986</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-0.8829225397593833</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-2.032599021712548</v>
+      </c>
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I5" s="6" t="inlineStr"/>
+      <c r="J5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>3.421381474697015</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>1.253436362427078</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>2.280545631451637</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>4.029940409581554</v>
+      </c>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="n">
+        <v>1.221151696327326</v>
+      </c>
+      <c r="I6" s="6" t="inlineStr"/>
+      <c r="J6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>10-50.000 hab</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>0,87</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-0,99</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-0,69</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-0,29</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>91,5%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-37,52%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>-32,96%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-25,58%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-0,7; 2,88</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-3,27; 1,42</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-2,94; 1,16</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-2,01; 1,23</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-60,92; —</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-80,94; 153,33</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-83,76; 157,27</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>0.873970569803866</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-0.9895260548321572</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-0.6888966147275587</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-0.2893888828684897</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.9149982761899946</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.375201706154917</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>-0.3295983542331891</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-0.255778069262947</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>0,35</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-0,94</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-0,78</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-0,22</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>37,63%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-32,51%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-49,98%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-9,05%</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-0.6968287581454635</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-3.265489270763104</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-2.94036298037003</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-2.007303046596869</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.6092436117233567</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.8093694641188283</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.8375959637971344</v>
+      </c>
+      <c r="J8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-1,63; 2,25</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-3,97; 1,73</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-2,66; 1,04</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-3,67; 2,8</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-83,23; 135,17</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-88,22; 495,2</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>2.875088794560838</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>1.421084302910772</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>1.156648351773769</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>1.232985329010222</v>
+      </c>
+      <c r="G9" s="6" t="inlineStr"/>
+      <c r="H9" s="6" t="n">
+        <v>1.533333492418238</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>1.572653601650879</v>
+      </c>
+      <c r="J9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Capitales</t>
+          <t>&gt;50.000 hab</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,197 +801,277 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-1,04</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-0,04</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0,11</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-0,18</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-57,01%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-3,96%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>10,2%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-23,24%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>0.3456629257406743</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-0.9419548120046566</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-0.7760155680676717</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-0.2208900349656196</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>0.3762902887674776</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-0.3250616083631738</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>-0.4998105698467687</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>-0.09048844674246916</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-2,91; 0,88</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-1,76; 1,49</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-1,42; 1,92</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-1,98; 1,03</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 497,35</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-1.62513496288346</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-3.969127014536483</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-2.66432237805079</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-3.667209955195928</v>
+      </c>
+      <c r="G11" s="6" t="inlineStr"/>
+      <c r="H11" s="6" t="n">
+        <v>-0.8323247698412375</v>
+      </c>
+      <c r="I11" s="6" t="inlineStr"/>
+      <c r="J11" s="6" t="n">
+        <v>-0.8821960313326861</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>2.250274213818543</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>1.727685952511223</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>1.042057951148157</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>2.804884267197604</v>
+      </c>
+      <c r="G12" s="6" t="inlineStr"/>
+      <c r="H12" s="6" t="n">
+        <v>1.351675202229185</v>
+      </c>
+      <c r="I12" s="6" t="inlineStr"/>
+      <c r="J12" s="6" t="n">
+        <v>4.951964553768907</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>-1.039954087189637</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-0.04079677024782929</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.1064932669415618</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-0.18421035654677</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.5701455299622866</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.03961271621502588</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>0.1020117540816276</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>-0.2323786302530023</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-2.914826508454189</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-1.761179876362646</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-1.421407713308881</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-1.982515614855572</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H14" s="6" t="inlineStr"/>
+      <c r="I14" s="6" t="inlineStr"/>
+      <c r="J14" s="6" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.8818875328288878</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>1.486186950169256</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>1.92146140534167</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>1.033723462674776</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>4.973523846157588</v>
+      </c>
+      <c r="H15" s="6" t="inlineStr"/>
+      <c r="I15" s="6" t="inlineStr"/>
+      <c r="J15" s="6" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>0,23</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-0,87</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-0,26</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-0,04</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>19,36%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-36,24%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>-19,05%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>-2,76%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-0,76; 1,12</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-2,07; 0,29</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-1,22; 0,58</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-1,28; 1,19</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-50,8; 155,5</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-66,55; 21,2</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-68,12; 70,29</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-63,21; 158,04</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>0.2282080865357068</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-0.8664410971725008</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-0.2577450495145029</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>-0.03898379982820721</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>0.1935507652937852</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>-0.3623918473207454</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>-0.1905077030765089</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>-0.0276275359358871</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-0.7577645490529157</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-2.068379759669225</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-1.221460862428278</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-1.277473350541076</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.5079826704178069</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.6654755826905576</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.6811564694751115</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-0.6321262122589971</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>1.124769700532271</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.2916933617014778</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.5849691601635552</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>1.191293429516993</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>1.555031496578238</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>0.2119609138976532</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>0.7029281085797116</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>1.580377024892609</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1108,14 +1079,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
